--- a/data/trans_bre/P1408-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P1408-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>-0,23</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>-15,64%</t>
         </is>
       </c>
     </row>
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,92; -1,07</t>
+          <t>-5,7; -1,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 2,45</t>
+          <t>-1,87; 2,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,98; -0,11</t>
+          <t>-4,63; -0,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 1,47</t>
+          <t>-1,84; 1,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -13,45</t>
+          <t>-100,0; -7,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 89,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-69,19; 278,47</t>
+          <t>-75,99; 244,59</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,06</t>
+          <t>-0,08</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-3,04%</t>
+          <t>-3,82%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 1,54</t>
+          <t>-3,91; 1,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,17; -0,42</t>
+          <t>-4,18; -0,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 0,43</t>
+          <t>-3,11; 0,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 1,43</t>
+          <t>-1,65; 1,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-58,16; 55,78</t>
+          <t>-58,87; 44,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-87,92; -3,88</t>
+          <t>-87,94; -0,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-82,18; 31,38</t>
+          <t>-81,72; 53,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-56,21; 129,74</t>
+          <t>-57,4; 138,71</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,04</t>
+          <t>-0,0</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-1,3%</t>
+          <t>-0,1%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,62; -0,95</t>
+          <t>-5,86; -0,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 1,08</t>
+          <t>-2,98; 1,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 1,44</t>
+          <t>-1,94; 1,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 2,03</t>
+          <t>-2,13; 2,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-95,6; -16,52</t>
+          <t>-96,09; -10,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-87,81; 100,7</t>
+          <t>-86,61; 126,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 309,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-51,19; 96,92</t>
+          <t>-47,71; 100,23</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,34</t>
+          <t>-0,53</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-32,83%</t>
+          <t>-13,82%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,33; -0,39</t>
+          <t>-5,07; -0,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 1,88</t>
+          <t>-3,07; 1,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 0,68</t>
+          <t>-3,24; 0,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 1,48</t>
+          <t>-3,25; 2,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-86,37; -0,13</t>
+          <t>-85,91; 7,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-70,1; 132,0</t>
+          <t>-69,5; 144,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-85,78; 64,05</t>
+          <t>-86,68; 73,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-71,33; 62,61</t>
+          <t>-59,74; 103,14</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,34</t>
+          <t>-0,26</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-17,21%</t>
+          <t>-14,32%</t>
         </is>
       </c>
     </row>
@@ -1060,27 +1060,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 3,99</t>
+          <t>-3,76; 4,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 0,42</t>
+          <t>-4,05; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 0,85</t>
+          <t>-4,01; 0,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 1,42</t>
+          <t>-2,37; 1,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-67,86; 177,26</t>
+          <t>-66,35; 202,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-73,78; 199,29</t>
+          <t>-72,22; 185,81</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0,97</t>
+          <t>-0,95</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-21,01%</t>
+          <t>-20,97%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 1,28</t>
+          <t>-3,23; 1,25</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,09; -0,85</t>
+          <t>-7,08; -0,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 2,49</t>
+          <t>-1,86; 2,35</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 1,36</t>
+          <t>-3,34; 1,43</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 188,38</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-95,99; -7,41</t>
+          <t>-94,6; -3,5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-82,46; 513,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-58,38; 40,77</t>
+          <t>-57,07; 46,43</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,15</t>
+          <t>0,64</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-5,36%</t>
+          <t>24,92%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 0,85</t>
+          <t>-3,28; 1,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 1,2</t>
+          <t>-1,13; 1,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 1,15</t>
+          <t>-1,76; 1,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 1,79</t>
+          <t>-0,91; 2,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-59,68; 24,6</t>
+          <t>-57,26; 41,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-71,91; 291,67</t>
+          <t>-69,89; 189,77</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-71,13; 120,37</t>
+          <t>-71,65; 110,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-62,1; 83,42</t>
+          <t>-29,38; 141,76</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,77</t>
+          <t>0,23</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>11,74%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 1,32</t>
+          <t>-2,52; 1,54</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 0,09</t>
+          <t>-2,33; 0,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 0,98</t>
+          <t>-1,41; 0,92</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 2,13</t>
+          <t>-1,15; 1,4</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-50,84; 41,1</t>
+          <t>-47,6; 46,03</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-90,9; 30,86</t>
+          <t>-90,65; 46,04</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-68,75; 120,4</t>
+          <t>-67,23; 112,03</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-27,69; 308,85</t>
+          <t>-41,69; 106,2</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,02</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,31; -0,53</t>
+          <t>-2,3; -0,61</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,65; -0,37</t>
+          <t>-1,59; -0,3</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,24; -0,05</t>
+          <t>-1,29; -0,03</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 0,76</t>
+          <t>-0,67; 0,72</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-50,09; -14,79</t>
+          <t>-50,59; -16,44</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-62,11; -18,5</t>
+          <t>-62,96; -15,06</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-55,12; -2,5</t>
+          <t>-57,23; -1,13</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-27,73; 37,78</t>
+          <t>-23,1; 32,4</t>
         </is>
       </c>
     </row>
